--- a/docs/Example Files/CRYSS V2.0 Input File Templates/7 Component Mixture.xlsx
+++ b/docs/Example Files/CRYSS V2.0 Input File Templates/7 Component Mixture.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\06 website\idiocratease-iggy.github.io\docs\Example Files\CRYSS V2.0 Input File Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CCFE79D-55F3-4A01-A73E-ED85917E7769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC93BAB-D537-461E-BCBD-1F9EA8A73EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5445" yWindow="1695" windowWidth="48060" windowHeight="15030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4020" yWindow="324" windowWidth="31980" windowHeight="16116" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="slice_records" sheetId="1" r:id="rId1"/>
+    <sheet name="CRYSS Input File V2.0" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -253,24 +253,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -278,12 +284,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -589,53 +589,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="22" width="14" customWidth="1"/>
     <col min="23" max="23" width="18" customWidth="1"/>
-    <col min="24" max="28" width="12.5703125" customWidth="1"/>
+    <col min="24" max="28" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="12"/>
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A1" s="8"/>
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="11" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="10" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="14" t="s">
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="16"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="18"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -701,26 +701,26 @@
       <c r="V2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="17" t="s">
+      <c r="W2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="X2" s="18" t="s">
+      <c r="X2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="Y2" s="18" t="s">
+      <c r="Y2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="Z2" s="18" t="s">
+      <c r="Z2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AA2" s="18" t="s">
+      <c r="AA2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="AB2" s="18" t="s">
+      <c r="AB2" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -748,7 +748,7 @@
       <c r="Z3" s="6"/>
       <c r="AB3" s="7"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -776,7 +776,7 @@
       <c r="Z4" s="6"/>
       <c r="AB4" s="7"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -804,7 +804,7 @@
       <c r="Z5" s="6"/>
       <c r="AB5" s="7"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -832,7 +832,7 @@
       <c r="Z6" s="6"/>
       <c r="AB6" s="7"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -860,7 +860,7 @@
       <c r="Z7" s="6"/>
       <c r="AB7" s="7"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -888,7 +888,7 @@
       <c r="Z8" s="6"/>
       <c r="AB8" s="7"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -916,7 +916,7 @@
       <c r="Z9" s="6"/>
       <c r="AB9" s="7"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -944,7 +944,7 @@
       <c r="Z10" s="6"/>
       <c r="AB10" s="7"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -972,7 +972,7 @@
       <c r="Z11" s="6"/>
       <c r="AB11" s="7"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1000,7 +1000,7 @@
       <c r="Z12" s="6"/>
       <c r="AB12" s="7"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1028,7 +1028,7 @@
       <c r="Z13" s="6"/>
       <c r="AB13" s="7"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1056,70 +1056,70 @@
       <c r="Z14" s="6"/>
       <c r="AB14" s="7"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="W15" s="5"/>
       <c r="X15" s="6"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="6"/>
       <c r="AB15" s="7"/>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="W16" s="5"/>
       <c r="X16" s="6"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="6"/>
       <c r="AB16" s="7"/>
     </row>
-    <row r="17" spans="23:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="23:28" x14ac:dyDescent="0.3">
       <c r="W17" s="5"/>
       <c r="X17" s="6"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="6"/>
       <c r="AB17" s="7"/>
     </row>
-    <row r="18" spans="23:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="23:28" x14ac:dyDescent="0.3">
       <c r="W18" s="5"/>
       <c r="X18" s="6"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="6"/>
       <c r="AB18" s="7"/>
     </row>
-    <row r="19" spans="23:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="23:28" x14ac:dyDescent="0.3">
       <c r="W19" s="5"/>
       <c r="X19" s="6"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="6"/>
       <c r="AB19" s="7"/>
     </row>
-    <row r="20" spans="23:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="23:28" x14ac:dyDescent="0.3">
       <c r="W20" s="5"/>
       <c r="X20" s="6"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="6"/>
       <c r="AB20" s="7"/>
     </row>
-    <row r="21" spans="23:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="23:28" x14ac:dyDescent="0.3">
       <c r="W21" s="5"/>
       <c r="X21" s="6"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="6"/>
       <c r="AB21" s="7"/>
     </row>
-    <row r="22" spans="23:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="23:28" x14ac:dyDescent="0.3">
       <c r="W22" s="5"/>
       <c r="X22" s="6"/>
       <c r="Y22" s="5"/>
       <c r="Z22" s="6"/>
       <c r="AB22" s="7"/>
     </row>
-    <row r="23" spans="23:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="23:28" x14ac:dyDescent="0.3">
       <c r="W23" s="5"/>
       <c r="X23" s="6"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="6"/>
       <c r="AB23" s="7"/>
     </row>
-    <row r="24" spans="23:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="23:28" x14ac:dyDescent="0.3">
       <c r="W24" s="5"/>
       <c r="X24" s="6"/>
       <c r="Y24" s="5"/>
